--- a/table3_rule.xlsx
+++ b/table3_rule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DICT\Desktop\Divide Rule\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66E88077-22DC-4D1D-9087-CF3A1EF4A4E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6A8EDE0-CC0E-467C-A094-3D86FE63E034}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -259,23 +259,27 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -370,10 +374,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
